--- a/data/google_news_dedup_29_0426_UTC_past2d.xlsx
+++ b/data/google_news_dedup_29_0426_UTC_past2d.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K56"/>
+  <dimension ref="A1:K55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -710,22 +710,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
+          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
+          <t>Amazon is expanding faster shipping with new 1-hour and 3-hour delivery options - MSN</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:25:21 GMT</t>
+          <t>Wed, 29 Apr 2026 12:14:50 GMT</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Z9IBmwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipANBVV95cUxPZW1hbE9CZGhEQmI1Rl9RdllkSjBlZUpla192b0Ruc0xCMVEtcVV2bE9uZkE4NEFrYnZLeHNrSzBwbnJZSmlHaUNhdFNvakdOTVYyYk1tYjluVWswVU0tbnhYN3RjaVRIS3RUNml5WWxMeU9uUE1Tdk9VVzB0MDJ4bnVLOVV1UXlvemcwazlic3RkS0FuYmxZSml1ZENUTVRfMzBzWFJLT1E2VDZjVmFjc09ZbmNWbFdBa2xzbWVDZkxOVWFNQTdfb3pXWnQyX1lnWFFBRkY1Z0RxVkVINWZQSUNhQUFxUlgzd1YwOEF5MmpsdXZvcDh0QS12dnFHMjZENXNMUmpNZjZTNlliVnNTUFBna3BoQmFib2Jadk53bDZjY0p4NG9CX05SMUIwR3NteF9wd2FSS2ctc01wclpEMTlMb214T3k0RGNzYzlsZmNtd2c4RW43bFRrLVpUQXRNakdvY0ZGNFMwZjRhNHBoR25YZFZGXzdQeUg1eHB2OTZ0dUxfSXc4dVp1R29BdFRNbER0bGMyNlE2RXItOFNOdzlsa3M?oc=5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -749,38 +749,38 @@
         </is>
       </c>
       <c r="K6" s="1" t="n">
-        <v>46141.30927083334</v>
+        <v>46141.51030092593</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>High Level City Belgium Dutch</t>
+          <t>BV Logistics Companies</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
+          <t>("Dropit" OR "DHL" OR "UPS" OR "DPD" OR "Flight Logistics" OR "Fedex" OR "Amazon" OR "Royal Mail" OR "Parcelforce" OR "EVRI" ) AND ( "supply " OR  "delivery") AND -"postal vote"</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ex-president van Zuid-Korea krijgt 7 jaar cel voor verzet tegen arrestatie - Nieuwsblad</t>
+          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Ex-president of South Korea gets 7 years in prison for resisting arrest - Nieuwsblad</t>
+          <t>Amazon unveils AI tools to reshape jobs and supply chains - dqindia.com</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:37:44 GMT</t>
+          <t>Wed, 29 Apr 2026 07:25:21 GMT</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNEVmWmR2V1c0MUhremREaXhqeW8yVjFRZ0ZjdXBGcFlJRXc4dTdMcFMxOFdCTXloZUJibVVHZU1RN0g2dlpoQ2tvX2tMWkdEUDFEQ01yUGpSS3c4MERhdnA4WTdUUDAtYWdnal8tS2x6LWM5d3BpTXRzSDRydHRwOHpNWTJtN0tSZjgweWNPNWhDR1R3NTh2YkRDdkRIWG56YS0zUUJQZ3c2bkxiQU5ZVlZuM3puQjhMVVpOYXhFa0R6MHg0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMimwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Z9IBmwFBVV95cUxOUnFmeEl1emRTem1lWVY1Q3ZkMUxvZEkzalAxVlNqNDRXMEJjbEZKVkprSFlpYWs2RzlWcDRJaUZJREhIMXpxWW1BcWdWZGI3NUZNS1ktOU1faENiaVZuRnUwcWhOY2pTMDlYWkZGWjZ2ZTYyTXlLWnZQTk42VEprYzVaalplbE91cnRya3BVVFBoY05xWlBVYlh3Zw?oc=5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -790,52 +790,52 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>nl</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>BE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>BE:nl</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K7" s="1" t="n">
-        <v>46141.44287037037</v>
+        <v>46141.30927083334</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>High Level City Belgium English</t>
+          <t>High Level City Belgium Dutch</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
+          <t>("Brussel" OR "Antwerpen" OR "Maastricht") AND (bom OR bommelding OR "verdacht pakket" OR "onbeheerd pakket" OR explosie OR schietpartij OR steekpartij OR liquidatie OR arrestatie)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
+          <t>Ex-president van Zuid-Korea krijgt 7 jaar cel voor verzet tegen arrestatie - Nieuwsblad</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
+          <t>Ex-president of South Korea gets 7 years in prison for resisting arrest - Nieuwsblad</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:32:15 GMT</t>
+          <t>Wed, 29 Apr 2026 10:37:44 GMT</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMlB6Y2pFTVNoRXdyNGxPdTVhdV9CZGdSeGxwaGx3aVVVaWcwNE5OZzV3cmVLeG9IWVVLQi1LSm9kTWdRQVA4ejROZGxySVF6QzAtSy1VbHhmWWgwcGJPUnN3TEZlcFRyMk9ITEJMaFdIckl1ek1VRmVtY0NqU0xnT1psblBuU19HY2NsZ1dpUy1FVDBGOTRsSVJnbmxDNVYtOEdySHJNOW5ZYThLVkw2SndGblVEa2hUSTB0UlJ5YnYzQXlRWWFDWVpUWEtNYkR5cExvOXZyV2UycjU0UHpYbW15MA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMixAFBVV95cUxNNEVmWmR2V1c0MUhremREaXhqeW8yVjFRZ0ZjdXBGcFlJRXc4dTdMcFMxOFdCTXloZUJibVVHZU1RN0g2dlpoQ2tvX2tMWkdEUDFEQ01yUGpSS3c4MERhdnA4WTdUUDAtYWdnal8tS2x6LWM5d3BpTXRzSDRydHRwOHpNWTJtN0tSZjgweWNPNWhDR1R3NTh2YkRDdkRIWG56YS0zUUJQZ3c2bkxiQU5ZVlZuM3puQjhMVVpOYXhFa0R6MHg0?oc=5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>nl</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -855,11 +855,11 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>BE:en</t>
+          <t>BE:nl</t>
         </is>
       </c>
       <c r="K8" s="1" t="n">
-        <v>46141.39739583333</v>
+        <v>46141.44287037037</v>
       </c>
     </row>
     <row r="9">
@@ -875,22 +875,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
+          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
+          <t>Hungary's Magyar visits Brussels seeking to unblock EU billions - Nonstop Local News</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:49:57 GMT</t>
+          <t>Wed, 29 Apr 2026 09:32:15 GMT</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ29yY0c5V0hkTW9obDNRdFV0aU5rSE9nbWQ2Yy05QngzRHR1QkxZMERtN1B6MHRyYzR4Y2lBSmk1eENIVDktNjEza2s4Xy1MV2paVlJmd21ibHBZUk9fLXZ4TDRnbEEyc05lTmtuMXdOU2ZwMTdlSmtLa05RTjNUcTJkbzc0c2RpeVpNR0ZZYXU?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi4wFBVV95cUxOMlB6Y2pFTVNoRXdyNGxPdTVhdV9CZGdSeGxwaGx3aVVVaWcwNE5OZzV3cmVLeG9IWVVLQi1LSm9kTWdRQVA4ejROZGxySVF6QzAtSy1VbHhmWWgwcGJPUnN3TEZlcFRyMk9ITEJMaFdIckl1ek1VRmVtY0NqU0xnT1psblBuU19HY2NsZ1dpUy1FVDBGOTRsSVJnbmxDNVYtOEdySHJNOW5ZYThLVkw2SndGblVEa2hUSTB0UlJ5YnYzQXlRWWFDWVpUWEtNYkR5cExvOXZyV2UycjU0UHpYbW15MA?oc=5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -914,7 +914,7 @@
         </is>
       </c>
       <c r="K9" s="1" t="n">
-        <v>46141.5346875</v>
+        <v>46141.39739583333</v>
       </c>
     </row>
     <row r="10">
@@ -930,22 +930,22 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
+          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
+          <t>EU plans crackdown on heavy fireworks after NL appeal - DutchNews.nl</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:14:10 GMT</t>
+          <t>Wed, 29 Apr 2026 12:49:57 GMT</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ3pQbnZaVFM2cnN6ZzZpMlk5WHlVZENiSkxJZmx5NzFWb2lkZHBIYVZGbzlWVlpISUpjQmFpSHJLTldrVGhBZ1RMQUZoSFJ4UU13OHczNmdxLThXRVJDOXZvSlVabDFSRER4bmVpQjYyWW8xdVl6MnNmRTFNdGRSTVNxTVk0Y3Zldm8wWEowTXRfZ0psNGdvVF90M0FnWGJw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMikAFBVV95cUxOZ29yY0c5V0hkTW9obDNRdFV0aU5rSE9nbWQ2Yy05QngzRHR1QkxZMERtN1B6MHRyYzR4Y2lBSmk1eENIVDktNjEza2s4Xy1MV2paVlJmd21ibHBZUk9fLXZ4TDRnbEEyc05lTmtuMXdOU2ZwMTdlSmtLa05RTjNUcTJkbzc0c2RpeVpNR0ZZYXU?oc=5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="K10" s="1" t="n">
-        <v>46141.42650462963</v>
+        <v>46141.5346875</v>
       </c>
     </row>
     <row r="11">
@@ -985,22 +985,22 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
+          <t>‘Total failure’: Leading economists tear into German federal budget - Brussels Signal</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:05:46 GMT</t>
+          <t>Wed, 29 Apr 2026 10:14:10 GMT</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQeW92M1I2ZGttX1FtVWRBaHRyZUtib3lhY0x5OUU4ZUsyUGxEc0RReW1PVFlFUzhsWmJGcEd0d0RaYXlvd0RYXzZVVVdfa0EzNlhzVXc3TE82OWxkS1ZwNDE5d0NBUy1KSGxkLV9EZ1NvZ0VpdnM0YnhWSkN6MHVnWDJPbjduNTNfajlCWW1ibURwTkkxdi1kV01scXBuVEd1cnQ3LWE0YUt3Zjd1ckRQeFFzcEdXdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxNQ3pQbnZaVFM2cnN6ZzZpMlk5WHlVZENiSkxJZmx5NzFWb2lkZHBIYVZGbzlWVlpISUpjQmFpSHJLTldrVGhBZ1RMQUZoSFJ4UU13OHczNmdxLThXRVJDOXZvSlVabDFSRER4bmVpQjYyWW8xdVl6MnNmRTFNdGRSTVNxTVk0Y3Zldm8wWEowTXRfZ0psNGdvVF90M0FnWGJw?oc=5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1024,7 +1024,7 @@
         </is>
       </c>
       <c r="K11" s="1" t="n">
-        <v>46141.5456712963</v>
+        <v>46141.42650462963</v>
       </c>
     </row>
     <row r="12">
@@ -1040,22 +1040,22 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
+          <t>British police arrest man after stabbing at least two people in north London - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:03:47 GMT</t>
+          <t>Wed, 29 Apr 2026 13:05:46 GMT</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOZXdHaHRaWDZsTWl5WGxHd0hteFdkYXRXYkQ5OHZOWGFKUGlLMVdPcm16VlNLQkxzNEhDZktIUjlqdExUejZyT0FZQTlJa3NMZWtWVTF6WnhfaWlhTVMzVXJEUEJ0dEdsR3FnU3gwX3F3Z3VwS0RkbDdhS19CUzdYQ1BVMm5meDlHaDBvMThOcXFvT2NKODNvY01vZXJVc3RnN0x5bU9rSXFrU2pCYzdLODNYaFdqYzRESTBXZVVaUjhrT1NmNUtXVEF6Z0oxY1A3VUJrY0IzaWZCTWwyS3ZldVBtYXNKYVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitgFBVV95cUxQeW92M1I2ZGttX1FtVWRBaHRyZUtib3lhY0x5OUU4ZUsyUGxEc0RReW1PVFlFUzhsWmJGcEd0d0RaYXlvd0RYXzZVVVdfa0EzNlhzVXc3TE82OWxkS1ZwNDE5d0NBUy1KSGxkLV9EZ1NvZ0VpdnM0YnhWSkN6MHVnWDJPbjduNTNfajlCWW1ibURwTkkxdi1kV01scXBuVEd1cnQ3LWE0YUt3Zjd1ckRQeFFzcEdXdw?oc=5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1079,38 +1079,38 @@
         </is>
       </c>
       <c r="K12" s="1" t="n">
-        <v>46141.54429398148</v>
+        <v>46141.5456712963</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>High Level City Belgium French</t>
+          <t>High Level City Belgium English</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
+          <t>("Brussels" OR "Antwerp" OR "Maastricht") AND (bomb OR explosion OR shooting OR stabbing OR "suspicious package" OR "bomb threat" OR "terror") AND -football AND -soccer AND -transfer</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Ponts de mai : explosion des réservations vers Aix et Marseille, le week-end du 8 mai bat des records ! - Maritima</t>
+          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>May bridges: explosion of reservations to Aix and Marseille, the weekend of May 8 breaks records! -Maritima</t>
+          <t>Brussels opens proceedings against Portugal for failing to carry out a road assessment of the main national roads - lnginnorthernbc.ca</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:13:00 GMT</t>
+          <t>Wed, 29 Apr 2026 13:03:47 GMT</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOdmtjTnZJeVR5aEVjUjNhejhEcklNNDQ4b0tzR2JyM2cwZlVIbV83UWNaWm02VkVxbk9KZml5NnZtc1NhVkRuci1FVi1CRS1RbVBiVWtXR1h1SVItU0pDelJnRTRXMEpfX3ZJM1hzTWliZm9hTnA2MHRsMUtmLXRZMWpFa0ZaRUNjaEgxbTQ3ZHd6aTVZaXJLLXhKWVZpd2g0R2w3Yng1UHFWTFQ3Q3BGVkFDMnkySDl6SC05TFZRZlJzUExnM0JxZ1duX1ZuSHZKTWduRFJFa2F6NTE5SjF4M3dsU1ZGZElfX25GZU1iVlRJQQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi5wFBVV95cUxOZXdHaHRaWDZsTWl5WGxHd0hteFdkYXRXYkQ5OHZOWGFKUGlLMVdPcm16VlNLQkxzNEhDZktIUjlqdExUejZyT0FZQTlJa3NMZWtWVTF6WnhfaWlhTVMzVXJEUEJ0dEdsR3FnU3gwX3F3Z3VwS0RkbDdhS19CUzdYQ1BVMm5meDlHaDBvMThOcXFvT2NKODNvY01vZXJVc3RnN0x5bU9rSXFrU2pCYzdLODNYaFdqYzRESTBXZVVaUjhrT1NmNUtXVEF6Z0oxY1A3VUJrY0IzaWZCTWwyS3ZldVBtYXNKYVE?oc=5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>fr</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1130,11 +1130,11 @@
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>BE:fr</t>
+          <t>BE:en</t>
         </is>
       </c>
       <c r="K13" s="1" t="n">
-        <v>46141.42569444444</v>
+        <v>46141.54429398148</v>
       </c>
     </row>
     <row r="14">
@@ -1150,22 +1150,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Patrick Bruel : « Il faut entendre les deux », le malaise d'Aurore Bergé face aux 18 accusatrices - Legossip.net</t>
+          <t>Patrick Bruel désormais visé par une enquête en Belgique - MSN</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Patrick Bruel: “You have to hear both”, Aurore Bergé’s discomfort in the face of the 18 accusers - Legossip.net</t>
+          <t>Patrick Bruel now targeted by investigation in Belgium - MSN</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 08:00:00 GMT</t>
+          <t>Wed, 29 Apr 2026 07:32:36 GMT</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSWhxTGVBQ0lHb05xc3JTTW9ZbjJmYkQxNnVQaktpNUNhWF9EMnpucUlPYTBGcjlwXzczTko3andjT0gtc1VkVUozRDhLU2hrSTYzeEdkNjVvcm9HRWUtUzR5MEZwalppRmhXVl9JbVJIRnc1NmFWMnhYcDdvQ0luM210TGdPRVJRRXliSVJPQmdHcFNzbmVpOWNEeUxmcS1jV1JGb2xvbDMxZ3Na?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinANBVV95cUxPRzZCMXdZWEpJWjgybnBQSW0wc19DZmVzTmJiTFJjTkxsMDFPOU5QdGp1QVJnc1VOVXhrNE5LM2JYRUNHRDZfT1JBYkxHdHY0MlpvdWFuZnEtb2tacGdIZUY0OHdNcnpnaEhwUnhERTJHTllGZ1VaZzZhNDRTX1dZTmVZaTVBdUJmZFptQmxCNk5oT0pmTXJtZDdWRFgzbHk1RUtCQ3pIY3JIYkQ1RHplQTlvWjExVEs3U1dtT2hDZ0VmLW5vVG9PbWVpNzd5M19kM19aMEtUQnZFVzhfQTJidEpVUEhESjBpcTZ5Yk9VRkg0YThhSDBoWEtkc0lFVW1Yc0lDd2hpSS1YTHdtSjNlTkRqNFVQVWhyeWpUaUQ0RnpNWm10WEY4QVhRNS1yYlJjd2gzOXBydDBCYno5VGcycFpua1BhZk8xVzJ5eHpIbmc4dmtsNUdCZlVEMDhQc2lXYzgtb3hVb2h1U2wwMFBBenNOa2M1ZkFBVGdrNGpmaF9QeWRhckUxblRMcms5a0pqMEV3TWUyWmw5SUM2?oc=5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1189,38 +1189,38 @@
         </is>
       </c>
       <c r="K14" s="1" t="n">
-        <v>46141.33333333334</v>
+        <v>46141.31430555556</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Visa pour la Flandre : Sporting Hasselt, le Wrexham flamand qui sent la buvette et le BV - Le Soir</t>
+          <t>Ponts de mai : explosion des réservations vers Aix et Marseille, le week-end du 8 mai bat des records ! - Maritima</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Visa for Flanders: Sporting Hasselt, the Flemish Wrexham that smells like a refreshment bar and BV - Le Soir</t>
+          <t>May bridges: explosion of reservations to Aix and Marseille, the weekend of May 8 breaks records! -Maritima</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:36:32 GMT</t>
+          <t>Wed, 29 Apr 2026 10:13:00 GMT</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMixgFBVV95cUxOMjNXQzFSNzdhVUdGbGpWTHJfazI3U2lNOThuWERXRHBtUTdTZkJhYXdobnNxRkFtaE9tT1JMN1dFZWI1NFBUb3gtQjJPS1NVdjk0Vks5TjNHMVNLRzRYRXJQWVZ0QlN6Wl93UjJGMHRQakx4RVp2SGplWm5Wd0NFZC13d2RFeFVnTS1jZVNJMXpGUm5WVXpYU2dtWEhnUzdwWGxCdFp1OTIxSlNlNjR2dnIxZHMzVHpYNWloUk9lS1gyclZZblE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi8gFBVV95cUxOdmtjTnZJeVR5aEVjUjNhejhEcklNNDQ4b0tzR2JyM2cwZlVIbV83UWNaWm02VkVxbk9KZml5NnZtc1NhVkRuci1FVi1CRS1RbVBiVWtXR1h1SVItU0pDelJnRTRXMEpfX3ZJM1hzTWliZm9hTnA2MHRsMUtmLXRZMWpFa0ZaRUNjaEgxbTQ3ZHd6aTVZaXJLLXhKWVZpd2g0R2w3Yng1UHFWTFQ3Q3BGVkFDMnkySDl6SC05TFZRZlJzUExnM0JxZ1duX1ZuSHZKTWduRFJFa2F6NTE5SjF4M3dsU1ZGZElfX25GZU1iVlRJQQ?oc=5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -1244,38 +1244,38 @@
         </is>
       </c>
       <c r="K15" s="1" t="n">
-        <v>46141.56703703704</v>
+        <v>46141.42569444444</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Local Town Maasmechelen French (fallback)</t>
+          <t>High Level City Belgium French</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken")</t>
+          <t>("Bruxelles" OR "Anvers" OR "Maastricht") AND (bombe OR explosion OR fusillade OR agression OR couteau OR "colis suspect" OR "alerte à la bombe" OR attentat) AND -football AND -transfert</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Pukkelpop - Pukkelpop divulgue 14 nouveaux noms à l'affiche du festival - DHnet</t>
+          <t>Patrick Bruel : « Il faut entendre les deux », le malaise d'Aurore Bergé face aux 18 accusatrices - Legossip.net</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Pukkelpop - Pukkelpop reveals 14 new names on the festival poster - DHnet</t>
+          <t>Patrick Bruel: “You have to hear both”, Aurore Bergé’s discomfort in the face of the 18 accusers - Legossip.net</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:04:00 GMT</t>
+          <t>Wed, 29 Apr 2026 08:00:00 GMT</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi4AFBVV95cUxOTWpFSXNCRUNRNUIyS0oyVTJYbUtwSGNsd1NEclpodlBjU2JjZklRSGdibUhBQS13SkpuUFVTR0w3WUdyc0lONTFLMTFlZEpZMTJDb0dKcWtqc1VUVUc5QTZEZER3Rm8wdm5uTGwyOHRXWk5sNnFLX25BSlpidVFXVTdYUVRWVnhjOUU4aHl1aVM5Vm1SMS1LUnJtaG4zVDFaenYtcnRoekM3cmN4aVVjRjgySEc5dmdKWjh0dlJCSHA0QlVsUFRKY3dUd2xKUlRNamNIN1Ytc25wVWduRFRFdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirAFBVV95cUxPSWhxTGVBQ0lHb05xc3JTTW9ZbjJmYkQxNnVQaktpNUNhWF9EMnpucUlPYTBGcjlwXzczTko3andjT0gtc1VkVUozRDhLU2hrSTYzeEdkNjVvcm9HRWUtUzR5MEZwalppRmhXVl9JbVJIRnc1NmFWMnhYcDdvQ0luM210TGdPRVJRRXliSVJPQmdHcFNzbmVpOWNEeUxmcS1jV1JGb2xvbDMxZ3Na?oc=5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1299,38 +1299,38 @@
         </is>
       </c>
       <c r="K16" s="1" t="n">
-        <v>46141.46111111111</v>
+        <v>46141.33333333334</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Village Wertheim (fallback)</t>
+          <t>Local Town Maasmechelen French</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
+          <t>("Maasmechelen" OR "Hasselt" OR "Lanaken") AND (manifestation OR bombe OR explosion OR fusillade OR couteau OR évacuation OR police OR arrestation OR protestation)</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
+          <t>Un individu impliqué dans une bagarre à Maasmechelen placé sous surveillance électronique - DHnet</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
+          <t>Individual involved in fight in Maasmechelen placed under electronic surveillance - DHnet</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:33:16 GMT</t>
+          <t>Wed, 29 Apr 2026 13:46:00 GMT</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNVl6N0kzWGpaUDZDUXlhZW44eTk4RHdiSjB4VmVUVkcyOFJ3SzM1b29hUVg4OWYway1OX3VxTzN2SElKMjhLRXpJSnVkOHB5T0hzRDcwUEVYcm5VYzdpVEhEZE5PTHlaSW13aXhVUlcyZXJkTkdDRDZ0dE9vUktkOElNbDJPVFI0aVJZUXlPSnZiOXRYUy02cWtuYmhybDNGbHdLbzJFOHdyekhOeHFkZ242ZWtIM0dib2hwdWFZeG5tT3VTWVdQZ3BSSDVNdmJGUERaalFBcDBtOEtqalZaYnk1UXlSTEdMUkhadDViUWY5REZQSzgwY2JPY2dtdw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_AFBVV95cUxPV3g3cTJpLUNzb0Q3cXF1X24yMUdtZTBwUExFZ09XWFVVaXgyREdDZDZfYVUtVWNhaWk0eFhLMG05OEE4TS1HYk1BXzZpZkRyMWpaQXRHMjlNZDl4ekNvZ21PTlJlOFhWaGVwM0NKX3NwSTc5aXNCUEVRZXJCZE83VUt6VDlKbWFjUi1HNXJ5MjdxekI0WkhoZXR0bF80ZUloSFM3UnV5NF96dmc4YlVjRjdMa05MVUZMOUpFMzdKX21qSkgxVDM2NTVBVEJSR0lBUDVDQWtwbWRGclN2b25nNWxQQ2p1NGFzSDF0Z0ZHY1NJOF9sMkJZMmprZEU?oc=5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1340,21 +1340,21 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>fr</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>BE</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>BE:fr</t>
         </is>
       </c>
       <c r="K17" s="1" t="n">
-        <v>46141.39810185185</v>
+        <v>46141.57361111111</v>
       </c>
     </row>
     <row r="18">
@@ -1370,22 +1370,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
+          <t>Roddick and Wertheim share caution around Alcaraz wrist injury : "I don’t think you ever question a player taking the long view with an injury" - Tennisuptodate.com</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:20:38 GMT</t>
+          <t>Wed, 29 Apr 2026 09:33:16 GMT</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQY01iZmJiZ1g0ZnoxcnZzUG5lUURqd1pSMFhkX214bFB1SFRJZElmTHdjUy1FNnpxbkVUVk5JNlY5NUlJRVRmS1E2TnkyaktsR2FDR3FEczBHRVViaUFUWDNMNlAxakpMNnRZeXQ0bG4zd1NRN2tGWGpQOWFybFlDeVNGUFBiS2FiSWFOalBGcFVLaDMyR2NIZDNKcTJBZ1AtTzdnQ2JRbUg2SUNqVGd5ekM0d2RKUmRlX2R0Z2daUzNDQ1FQX3Znck9VcUJkSHVOR2t4d0VFVzZLR2hWYnQyNnNSMVZhQWxvdVVYQ3ExeVBGMHhOSW4zYkZCSFBfdG9SdGU5WVQzMHEzLXJDRnNhOUZqYlU2TGNTS19KM2pORHBJclBSdzZNWUtxZURZeVRxb1c0ckU5cExWV1VUa0ExMVlnRUdnOUFodlJjWElpTzlmckNFbERES1dBelluZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi_gFBVV95cUxNNVl6N0kzWGpaUDZDUXlhZW44eTk4RHdiSjB4VmVUVkcyOFJ3SzM1b29hUVg4OWYway1OX3VxTzN2SElKMjhLRXpJSnVkOHB5T0hzRDcwUEVYcm5VYzdpVEhEZE5PTHlaSW13aXhVUlcyZXJkTkdDRDZ0dE9vUktkOElNbDJPVFI0aVJZUXlPSnZiOXRYUy02cWtuYmhybDNGbHdLbzJFOHdyekhOeHFkZ242ZWtIM0dib2hwdWFZeG5tT3VTWVdQZ3BSSDVNdmJGUERaalFBcDBtOEtqalZaYnk1UXlSTEdMUkhadDViUWY5REZQSzgwY2JPY2dtdw?oc=5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="K18" s="1" t="n">
-        <v>46141.51432870371</v>
+        <v>46141.39810185185</v>
       </c>
     </row>
     <row r="19">
@@ -1425,22 +1425,22 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
+          <t>Copter Rescues Teen Stuck In Mud At Wertheim National Refuge - MSN</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:00:00 GMT</t>
+          <t>Wed, 29 Apr 2026 12:20:38 GMT</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQa0FxVGR6Zkxyd2IxX2cyV3N4WnlRSGxTVmZjbktUOTE4NkwwNHJPNVVBNndjZ0dqTU9rb3phWkhrNFVrdHpGXzBORzdJVFFacU9Lem5YRXN2YlNOTFN1c2VSVjM3VTJUTzlWNFlFaXY1ZzVGZF9MdmVrbmNWc1RfQmpnZDdlakVr0gGIAUFVX3lxTE42aW1SaTV3aUtTRnFMYi1mVmZMR1hGN1dvZUxGdGNfRmVwT0gyel9oNm5Kek9LT19tOS1aeERhS05XaE5EVi1HQlVyYVRfVEQ4anBqeUQ0NUdKS2lZQUNxbHFnWlFtOV9qRnltMlFjUm1TdzZhR2NjUkhDWDRveTZFVDNBLTM3REM?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi3gJBVV95cUxQY01iZmJiZ1g0ZnoxcnZzUG5lUURqd1pSMFhkX214bFB1SFRJZElmTHdjUy1FNnpxbkVUVk5JNlY5NUlJRVRmS1E2TnkyaktsR2FDR3FEczBHRVViaUFUWDNMNlAxakpMNnRZeXQ0bG4zd1NRN2tGWGpQOWFybFlDeVNGUFBiS2FiSWFOalBGcFVLaDMyR2NIZDNKcTJBZ1AtTzdnQ2JRbUg2SUNqVGd5ekM0d2RKUmRlX2R0Z2daUzNDQ1FQX3Znck9VcUJkSHVOR2t4d0VFVzZLR2hWYnQyNnNSMVZhQWxvdVVYQ3ExeVBGMHhOSW4zYkZCSFBfdG9SdGU5WVQzMHEzLXJDRnNhOUZqYlU2TGNTS19KM2pORHBJclBSdzZNWUtxZURZeVRxb1c0ckU5cExWV1VUa0ExMVlnRUdnOUFodlJjWElpTzlmckNFbERES1dBelluZw?oc=5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="K19" s="1" t="n">
-        <v>46141.375</v>
+        <v>46141.51432870371</v>
       </c>
     </row>
     <row r="20">
@@ -1480,22 +1480,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
+          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
+          <t>Miami top stories: Women-owned businesses, philanthropist’s death, Charlamagne - Miami Herald</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:29:30 GMT</t>
+          <t>Wed, 29 Apr 2026 09:00:00 GMT</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUUEycjNGSThwMW5EVGFHTkotMVdUYjNwY0xiWWJzU19tQmVoX0k4R195QVlaUEltVDFSN2NISXp0Ynp6TWZpTHdWeUtzWHRHTFBpTTdVOVhfZHFfTzlJdWlxTFktcTNqRVMydmhNcWJhWEtFMVBGZ1cwT3NfUFptemp0UjRMM19nc1gycUlHajZaV1lRNUZmSXpObWNBRV80QXBBT0RRSkp3c0RfOUlGMXA2VFdObXJmLXo1TWFKRi10eVk?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiiAFBVV95cUxQa0FxVGR6Zkxyd2IxX2cyV3N4WnlRSGxTVmZjbktUOTE4NkwwNHJPNVVBNndjZ0dqTU9rb3phWkhrNFVrdHpGXzBORzdJVFFacU9Lem5YRXN2YlNOTFN1c2VSVjM3VTJUTzlWNFlFaXY1ZzVGZF9MdmVrbmNWc1RfQmpnZDdlakVr0gGIAUFVX3lxTE42aW1SaTV3aUtTRnFMYi1mVmZMR1hGN1dvZUxGdGNfRmVwT0gyel9oNm5Kek9LT19tOS1aeERhS05XaE5EVi1HQlVyYVRfVEQ4anBqeUQ0NUdKS2lZQUNxbHFnWlFtOV9qRnltMlFjUm1TdzZhR2NjUkhDWDRveTZFVDNBLTM3REM?oc=5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1519,38 +1519,38 @@
         </is>
       </c>
       <c r="K20" s="1" t="n">
-        <v>46141.31215277778</v>
+        <v>46141.375</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Local Town Ingolstadt German</t>
+          <t>Village Wertheim (fallback)</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
+          <t>("Wertheim Village" OR "Wertheim") AND (shopping OR outlet OR luxury OR retail OR news)</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Polizei- und Feuerwehrmeldungen am 29.04.2026 aus Bayern - Newsflash24</t>
+          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Police and fire brigade reports from Bavaria on April 29, 2026 - Newsflash24</t>
+          <t>Rafael Jodar surpasses Big 3, Sinner and Alcaraz with historic start to ATP career - Tennis Tonic</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 06:49:46 GMT</t>
+          <t>Wed, 29 Apr 2026 07:29:30 GMT</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUmV5UC1NZV92Y0VpLTlWMFFjYW42aHdscXVTS0daeGN3c3h5cWJUWFJPckRWNWVaR0Q5OWNUY0lORkJLWWZueDgwZjZBOURCMlNyYkVMbWY4a0hvUWpKWHhabHFtZ1hkZTk5Rmp6T3pGMHhpTHc2MnV1Ny1hdDVJMDZ0Z3EyYzhwcndINnRXMVhXcE8zX3FiZ2lORS0?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiwwFBVV95cUxOUUEycjNGSThwMW5EVGFHTkotMVdUYjNwY0xiWWJzU19tQmVoX0k4R195QVlaUEltVDFSN2NISXp0Ynp6TWZpTHdWeUtzWHRHTFBpTTdVOVhfZHFfTzlJdWlxTFktcTNqRVMydmhNcWJhWEtFMVBGZ1cwT3NfUFptemp0UjRMM19nc1gycUlHajZaV1lRNUZmSXpObWNBRV80QXBBT0RRSkp3c0RfOUlGMXA2VFdObXJmLXo1TWFKRi10eVk?oc=5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -1560,52 +1560,52 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K21" s="1" t="n">
-        <v>46141.28456018519</v>
+        <v>46141.31215277778</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Village Bicester Kildare</t>
+          <t>Local Town Ingolstadt German</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
+          <t>("Ingolstadt") AND (Protest OR Bombe OR Bombendrohung OR Explosion OR Schießerei OR Polizei OR Evakuierung OR Terrorverdacht) AND -Audi AND -Auto AND -Wetter</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
+          <t>Polizei- und Feuerwehrmeldungen am 29.04.2026 aus Bayern - Newsflash24</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
+          <t>Police and fire brigade reports from Bavaria on April 29, 2026 - Newsflash24</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 08:43:31 GMT</t>
+          <t>Wed, 29 Apr 2026 06:49:46 GMT</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNQmZMOFBsemJmaDBsSTBkMXByTUNENW0yU1JDVGQ1dC1VREhyU1lXdGpOS1VmdDFWVXJjQjdmSkZQN3cxazRuS2M4bkl5N2hZLWZ1MEkySXVhT2tZS1BiNXZXbmdvdzVtRHNvdEN5dTZVQU9PVXNBaXdCMnl1WGExNnllLU9lbFNMbnRpSDQzSFg0TVhsMlFJQVVlbTRpN1JZTlotRVpYa2d0UnRLVXZfYTB3WXRyUGs0V0t1NTlFX2ZiVDdwSlN6ZXBPYm5uX3h4eG84UHVYc2FFdGJtdmhvNFpIRmxkblNjYjNMMEhJbV9SUG5zUHlFeUwwM1VuTWJtT3hzQ0d3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxQUmV5UC1NZV92Y0VpLTlWMFFjYW42aHdscXVTS0daeGN3c3h5cWJUWFJPckRWNWVaR0Q5OWNUY0lORkJLWWZueDgwZjZBOURCMlNyYkVMbWY4a0hvUWpKWHhabHFtZ1hkZTk5Rmp6T3pGMHhpTHc2MnV1Ny1hdDVJMDZ0Z3EyYzhwcndINnRXMVhXcE8zX3FiZ2lORS0?oc=5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -1615,52 +1615,52 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K22" s="1" t="n">
-        <v>46141.36355324074</v>
+        <v>46141.28456018519</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>High Level City UK Ireland</t>
+          <t>Village Bicester Kildare</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>("Dublin" OR "Oxford" OR "London") AND ("Bomb" OR "explosion" OR "shooting"  OR "Stabbing" OR "suspicious package" OR "unattended Package" OR "explosive" OR "bomb threat" OR "Protest" OR "blockade" )</t>
+          <t>("Bicester Village" OR "Kildare Village" OR "Bicester outlet" OR "Kildare outlet")</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
+          <t>Why coachloads of Chinese tourists are flocking to your favourite beauty spot - MSN</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:59:39 GMT</t>
+          <t>Wed, 29 Apr 2026 08:43:31 GMT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVFlwcFBZallGZzJVVjVmeWxtMUt4cE44SkxKYTFfbUlOZUQyUG9mSTVmUmlzZm5vVXBWSG9USDJFb1J0LVJScjdnRnJMb2FSMmNLMnpXbnJBMzJQWlJRaHBXbXZMZEJUMzJaVnBSaGJ4eEx2Nm5Od1VGMVhETUxreFJocTRQTlhrdWhTUlRKZXNuR3lXUlV5aTY0c2lNUEVUZ1dkMEg0SFBPREN0b1IzOFplQ3NJanN4MDI1Tw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMihgJBVV95cUxNQmZMOFBsemJmaDBsSTBkMXByTUNENW0yU1JDVGQ1dC1VREhyU1lXdGpOS1VmdDFWVXJjQjdmSkZQN3cxazRuS2M4bkl5N2hZLWZ1MEkySXVhT2tZS1BiNXZXbmdvdzVtRHNvdEN5dTZVQU9PVXNBaXdCMnl1WGExNnllLU9lbFNMbnRpSDQzSFg0TVhsMlFJQVVlbTRpN1JZTlotRVpYa2d0UnRLVXZfYTB3WXRyUGs0V0t1NTlFX2ZiVDdwSlN6ZXBPYm5uX3h4eG84UHVYc2FFdGJtdmhvNFpIRmxkblNjYjNMMEhJbV9SUG5zUHlFeUwwM1VuTWJtT3hzQ0d3?oc=5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -1684,7 +1684,7 @@
         </is>
       </c>
       <c r="K23" s="1" t="n">
-        <v>46141.49975694445</v>
+        <v>46141.36355324074</v>
       </c>
     </row>
     <row r="24">
@@ -1700,22 +1700,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
+          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
+          <t>Footage appears to show person being arrested in London after Golders Green stabbing - Sky News</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:58:00 GMT</t>
+          <t>Wed, 29 Apr 2026 11:59:39 GMT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaUI1MW81X2g2ZDEyeHpzajNkOE1WV0c4Vk10dnRFak1ENWNDRFFXWDVMdUI5VTI3TTI5S29fbHZCV01jSVNUa0xhZmladzFfcWt3VS04V2JSM2RHSjExRjRmQ2FOWnp2dkRDcU41LVk0d3MyMHZYU1hSRm4zOUo0YlJGWlB5aVNhUEx0TDM0V2F6V0Zta2c?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMivAFBVV95cUxPVFlwcFBZallGZzJVVjVmeWxtMUt4cE44SkxKYTFfbUlOZUQyUG9mSTVmUmlzZm5vVXBWSG9USDJFb1J0LVJScjdnRnJMb2FSMmNLMnpXbnJBMzJQWlJRaHBXbXZMZEJUMzJaVnBSaGJ4eEx2Nm5Od1VGMVhETUxreFJocTRQTlhrdWhTUlRKZXNuR3lXUlV5aTY0c2lNUEVUZ1dkMEg0SFBPREN0b1IzOFplQ3NJanN4MDI1Tw?oc=5</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
@@ -1739,7 +1739,7 @@
         </is>
       </c>
       <c r="K24" s="1" t="n">
-        <v>46141.45694444444</v>
+        <v>46141.49975694445</v>
       </c>
     </row>
     <row r="25">
@@ -1755,22 +1755,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
+          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
+          <t>Fourth man arrested after 'stabbing' at Oxford park - Oxford Mail</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:52:24 GMT</t>
+          <t>Wed, 29 Apr 2026 10:58:00 GMT</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0EycGxDaGFfdUd0ODVhLTJBcnBzaGxpbDJSVm9NME91MVpiZFFqbTFCcEttRGFGRHFpTG16SFFYZHBRcTQxeEN3bW9IM3dsZXB4U3lhZE5xbWdHZjVhVThpWnZYZU1iU2FNWHJGSWNMRmE4bVpfdHpWQ0Nwd0dicldSTlZpVVNHb3pJS192Vmk2UEU3U3plQmhWZXI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMilgFBVV95cUxPaUI1MW81X2g2ZDEyeHpzajNkOE1WV0c4Vk10dnRFak1ENWNDRFFXWDVMdUI5VTI3TTI5S29fbHZCV01jSVNUa0xhZmladzFfcWt3VS04V2JSM2RHSjExRjRmQ2FOWnp2dkRDcU41LVk0d3MyMHZYU1hSRm4zOUo0YlJGWlB5aVNhUEx0TDM0V2F6V0Zta2c?oc=5</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -1794,7 +1794,7 @@
         </is>
       </c>
       <c r="K25" s="1" t="n">
-        <v>46141.45305555555</v>
+        <v>46141.45694444444</v>
       </c>
     </row>
     <row r="26">
@@ -1810,22 +1810,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Woman guilty of murdering sister after stabbing her 10 times and stealing Rolex - London Now</t>
+          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Woman guilty of murdering sister after stabbing her 10 times and stealing Rolex - London Now</t>
+          <t>Appeal launched after violent park altercation leaves man stabbed - London Now</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:14:54 GMT</t>
+          <t>Wed, 29 Apr 2026 10:52:24 GMT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMingFBVV95cUxPSnZ0WTZ5a0Y3QnBIRGRRMlhSYlZWVlF4SjNYWGFoUm5xM3FnX0w3c3NpSGU3eUQtaDZ5VS1NN2dYM1lpRTk4MndMTmpJLUI1S3FkSUhsajRVNUdRMWlsdUtPWmZycDZvOVpSRF9MLWtwa096V2hsMEM1ejFFdGFvdmRlbFVtSzhuRTZiYmJNM2dtZWs4Q0dNN3UyaU42Zw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxPX0EycGxDaGFfdUd0ODVhLTJBcnBzaGxpbDJSVm9NME91MVpiZFFqbTFCcEttRGFGRHFpTG16SFFYZHBRcTQxeEN3bW9IM3dsZXB4U3lhZE5xbWdHZjVhVThpWnZYZU1iU2FNWHJGSWNMRmE4bVpfdHpWQ0Nwd0dicldSTlZpVVNHb3pJS192Vmk2UEU3U3plQmhWZXI?oc=5</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
@@ -1849,7 +1849,7 @@
         </is>
       </c>
       <c r="K26" s="1" t="n">
-        <v>46141.46868055555</v>
+        <v>46141.45305555555</v>
       </c>
     </row>
     <row r="27">
@@ -1975,22 +1975,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
+          <t>Bandiere d'Israele e urla di "schifo": scintille in consiglio sul 25 aprile. "Ebrei esclusi, non accadeva dal 1938" - MilanoToday</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Strike at Fluid-o-Tech against the dismissal of Gianfranco, who underwent knee surgery - Il Giorno</t>
+          <t>Israeli flags and shouts of "disgust": sparks in the council on April 25th. "Jews excluded, this hasn't happened since 1938" - MilanoToday</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:31:55 GMT</t>
+          <t>Wed, 29 Apr 2026 09:58:16 GMT</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBkYmpTaUtZRzJOT2dvZmpkUlRCZHplbnVCOVVfOUFyNEN5bFlRMUZaR2JkM3dHeUY0NG92cS1wTUlQT291Ulpzcl9WclBCUEdoNWp1Rk5LenJkSy11Q2RnNEo1bE8zNFpZNTRZX2JyRjF5U3ZrSW9VUg?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOR0VfRG1nTDEzQ3FtanNyaU4xUGd1aTdFR0EtUE9XaUxBYmN1Snh6S2hoTmpUS1hNZ3ItRHRqZzJwelR1SEIxMnFfSXBXQXFpODAzbksyNXFIZnFORFp6TWpKSTA2d3VLN1dBWXgzcEt4blYxNWZRa0VsSzEwN3lWcWNobWx4R19odUNkeHRXOA?oc=5</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2014,7 +2014,7 @@
         </is>
       </c>
       <c r="K29" s="1" t="n">
-        <v>46141.48049768519</v>
+        <v>46141.41546296296</v>
       </c>
     </row>
     <row r="30">
@@ -2030,22 +2030,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
+          <t>Sciopero alla Fluid-o-Tech contro il licenziamento di Gianfranco, operato al ginocchio - Il Giorno</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
+          <t>Strike at Fluid-o-Tech against the dismissal of Gianfranco, who underwent knee surgery - Il Giorno</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:00:29 GMT</t>
+          <t>Wed, 29 Apr 2026 11:31:55 GMT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMieEFVX3lxTFBkYmpTaUtZRzJOT2dvZmpkUlRCZHplbnVCOVVfOUFyNEN5bFlRMUZaR2JkM3dHeUY0NG92cS1wTUlQT291Ulpzcl9WclBCUEdoNWp1Rk5LenJkSy11Q2RnNEo1bE8zNFpZNTRZX2JyRjF5U3ZrSW9VUg?oc=5</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -2069,7 +2069,7 @@
         </is>
       </c>
       <c r="K30" s="1" t="n">
-        <v>46141.50033564815</v>
+        <v>46141.48049768519</v>
       </c>
     </row>
     <row r="31">
@@ -2085,22 +2085,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Bandiere d'Israele e urla di "schifo": scintille in consiglio sul 25 aprile. "Ebrei esclusi, non accadeva dal 1938" - MilanoToday</t>
+          <t>Primo maggio 2026, cosa fare a Milano? Corteo, sagre, eventi da non perdere - Mentelocale</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Israeli flags and shouts of "disgust": sparks in the council on April 25th. "Jews excluded, this hasn't happened since 1938" - MilanoToday</t>
+          <t>May 1st 2026, what to do in Milan? Procession, festivals, events not to be missed - Mentelocale</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:58:16 GMT</t>
+          <t>Wed, 29 Apr 2026 12:00:29 GMT</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMijwFBVV95cUxOR0VfRG1nTDEzQ3FtanNyaU4xUGd1aTdFR0EtUE9XaUxBYmN1Snh6S2hoTmpUS1hNZ3ItRHRqZzJwelR1SEIxMnFfSXBXQXFpODAzbksyNXFIZnFORFp6TWpKSTA2d3VLN1dBWXgzcEt4blYxNWZRa0VsSzEwN3lWcWNobWx4R19odUNkeHRXOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMitwFBVV95cUxQS1BiR3paQlFRY2dNZFhYTHp0S3BwWjIxT2YyMjgwZGZnMmNONkdXa2ItUktveS16SVVneDFSSU9qbjhHSEJ3SnBlYXEyaC1VZm5BVERYSHlCcjZPNElOMjc5bTJHbDB6amFXWUZKLXdPdHJjaFdFbmxPYk1NZDRNOVNGLTZGeV92XzFkaEZpTTZxaW0zYnRrRVVmUlc3a2wwWERPYU92NFJKSUY5b1JzU0tpMzdQUFE?oc=5</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="K31" s="1" t="n">
-        <v>46141.41546296296</v>
+        <v>46141.50033564815</v>
       </c>
     </row>
     <row r="32">
@@ -2790,32 +2790,32 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Access Disruption Wertheim English (fallback)</t>
+          <t>Access Disruption Ingolstadt German</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Stars who smoke—and the reactions they sparked - MSN</t>
+          <t>Heftiger A9-Unfall bei Schweitenkirchen: 23-Jähriger überschlägt sich nach Crash - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Stars who smoke—and the reactions they sparked - MSN</t>
+          <t>Violent A9 accident near Schweitenkirchen: 23-year-old rolls over after crash - Pfaffenhofen Today</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:33:37 GMT</t>
+          <t>Wed, 29 Apr 2026 13:28:11 GMT</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMinAFBVV95cUxNYnNJLVMxdjZzbUZYaXcyRjBqb1dSNkd1aVp2VzlpaTJCdVlnZVF0bE0zT2hxLXZQeFZYUU1Bc2l6Q0lMQi1QSTNLT0x5RmFzSmlSQTJsWVQzQmNpLWdVc2tPWk1NMTFnY2VfNk9rdkpFNWJhV2JITnhuTktoVk01NHFVRDcyS0lkT0pKRXpCMDJycjRjc0JaODI4eUI?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9CRlpfdmJHTkxyMmtPNVk0S2hEQ2F6UUNRazBTZ21vMzJTTlRnUzBzTHlURkNnQ1hZaHJ6SmpSUkRiMmFGaVVfLW1aVXdnSXEwSzFRQ2dkTkhFVTJpZDhjaUI5eTdQZGtHT2ptYQ?oc=5</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2825,52 +2825,52 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K44" s="1" t="n">
-        <v>46141.31501157407</v>
+        <v>46141.56123842593</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Access Disruption Wertheim English (fallback)</t>
+          <t>Access Disruption Ingolstadt German</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>("Wertheim" OR "A3 autobahn" OR "Würzburg" OR "Aschaffenburg")</t>
+          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Andy Roddick shares ESPN ultimatum - MSN</t>
+          <t>News of the day vom 29.04.2026: Verheerender Wohnungsbrand in Nürnberg Reichelsdorf - eine Person verstorben - Franken Fernsehen</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Andy Roddick shares ESPN ultimatum - MSN</t>
+          <t>News of the day from April 29, 2026: Devastating apartment fire in Nuremberg Reichelsdorf - one person died - Franken Fernsehen</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:45:28 GMT</t>
+          <t>Wed, 29 Apr 2026 11:13:37 GMT</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi5wJBVV95cUxNb0g4U0Z6TkFLQ0tPMzByNzJpU2RmTkxZbk1lUEZqaURySzA2bnpsbFNSTU1YeVFUSEk5QXAwWHc5Vk44YUdtLWs3T09mTkxiejh3LUhuUU5vbUh5ZHczbnF0eEotWWdJandqVkZEWEczbmFzNW8zQkdNR291a3VPNWRrMGE1eTh5SXBtb0pRbFo4ajBGcFpOSkFsckZER0lJV3E2blRDQzh2SlJ2UGdhUzBDRDhsNVY5eHVWb2REOUVLTTdsWldhd284d0NvRklBU0FrcHduUUJSZjBjbXI2SEZwRGVPZXZ5SkxFMmdvel9CUnNrZjZXYnFYZjZ2Q2NCbVZqb3BnRVRHdWd6Tjg5bzIyQzJGUDhCenNlaFVwel9HelhpVXotZ1oyUk5xeXF2SXlnc0hvSTBLLVhfRG1TVTFyNnltZ2hzQzJvNFJPS1NXM2xydWtsVUlEVVVCck0zblJvUGNDOA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNclRsZ045YVdyWk9BY2g3cll0ZExmOURkZnpKYnRGWmV5Y05oVnJVSHZyS0FMVkRZenFLeThfMDdHWUJEcUJzRFhLR05YVF9nOWJwYVlBTEpRR1gyaGxqNjFKT3NTeEVpdWM5U2t5YUN4eFluS0JoekNhXzV1YlFPdTlXTEFrY29yTFZ3dmJmVmd5ZXhHbVVMMUZyWURyZUwzak1ySl93UkRXUjhoZ3Z4U3N3LVdaTmlIcTRLSkc5Rkd2bnVmS0R4V2N0anh0R3JXeFl4eHF1dUJDQ00yN2loRGpKcUFJV2RZY2Zn?oc=5</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2880,21 +2880,21 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>en-GB</t>
+          <t>de</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>GB</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>GB:en</t>
+          <t>DE:de</t>
         </is>
       </c>
       <c r="K45" s="1" t="n">
-        <v>46141.32324074074</v>
+        <v>46141.46778935185</v>
       </c>
     </row>
     <row r="46">
@@ -2910,22 +2910,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Heftiger A9-Unfall bei Schweitenkirchen: 23-Jähriger überschlägt sich nach Crash - Pfaffenhofen Today</t>
+          <t>Auffahrunfall auf A8 bei Leonberg führt zu Zeugensuche - AsatuNews.co.id</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Violent A9 accident near Schweitenkirchen: 23-year-old rolls over after crash - Pfaffenhofen Today</t>
+          <t>Rear-end collision on A8 near Leonberg leads to search for witnesses - AsatuNews.co.id</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 13:28:11 GMT</t>
+          <t>Wed, 29 Apr 2026 11:58:41 GMT</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMibEFVX3lxTE9CRlpfdmJHTkxyMmtPNVk0S2hEQ2F6UUNRazBTZ21vMzJTTlRnUzBzTHlURkNnQ1hZaHJ6SmpSUkRiMmFGaVVfLW1aVXdnSXEwSzFRQ2dkTkhFVTJpZDhjaUI5eTdQZGtHT2ptYQ?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE04SGV5SWFVcWllYWVpcDluNHhaLTlJSU5Jamw5Q192YklxWnByNFp6RDFXRzBzYUE1dnZvUjVvTnJWWjdPUlpKLVFmTWloRjJHbmFkb1FBQjF1QjU0NktYT1pVUWJkTzNPWGtuSk0xZG0zZw?oc=5</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="K46" s="1" t="n">
-        <v>46141.56123842593</v>
+        <v>46141.49908564815</v>
       </c>
     </row>
     <row r="47">
@@ -2965,22 +2965,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>News of the day vom 29.04.2026: Verheerender Wohnungsbrand in Nürnberg Reichelsdorf - eine Person verstorben - Franken Fernsehen</t>
+          <t>Wegen Unfall auf A9: Sperrung zwischen Siders-Ost und Siders-West - Unfallmeldungen.ch</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>News of the day from April 29, 2026: Devastating apartment fire in Nuremberg Reichelsdorf - one person died - Franken Fernsehen</t>
+          <t>Due to an accident on the A9: closure between Siders-East and Siders-West - accident reports.ch</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:13:37 GMT</t>
+          <t>Wed, 29 Apr 2026 10:39:16 GMT</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi6wFBVV95cUxNclRsZ045YVdyWk9BY2g3cll0ZExmOURkZnpKYnRGWmV5Y05oVnJVSHZyS0FMVkRZenFLeThfMDdHWUJEcUJzRFhLR05YVF9nOWJwYVlBTEpRR1gyaGxqNjFKT3NTeEVpdWM5U2t5YUN4eFluS0JoekNhXzV1YlFPdTlXTEFrY29yTFZ3dmJmVmd5ZXhHbVVMMUZyWURyZUwzak1ySl93UkRXUjhoZ3Z4U3N3LVdaTmlIcTRLSkc5Rkd2bnVmS0R4V2N0anh0R3JXeFl4eHF1dUJDQ00yN2loRGpKcUFJV2RZY2Zn?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNaDdvdlU1NHFzOVd1VUZDSGlNUmhYQ2pDYXRpeDVJSDBsQmZXY2tfUlZsNWtjY3BvTHJadnZaTVQwNVE4X2xGV2RoQ24yVkx3cG5XckhNblhZZExhMVVEX3JhbFBuS1NiU2NqYnVfVk5ZVWdERW81SnZSeWFvV3lLY1VkWHZGODhNT01QNkZ3R2NscjhnOWh0aEdzaVM0eTRHemNpN3R3?oc=5</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3004,7 +3004,7 @@
         </is>
       </c>
       <c r="K47" s="1" t="n">
-        <v>46141.46778935185</v>
+        <v>46141.44393518518</v>
       </c>
     </row>
     <row r="48">
@@ -3020,22 +3020,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Auffahrunfall auf A8 bei Leonberg führt zu Zeugensuche - AsatuNews.co.id</t>
+          <t>Wegen Unfall auf A2: Verkehrsbehinderung zwischen Beckenried und Buochs - Unfallmeldungen.ch</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Rear-end collision on A8 near Leonberg leads to search for witnesses - AsatuNews.co.id</t>
+          <t>Due to an accident on the A2: traffic obstruction between Beckenried and Buochs ​​- accident reports.ch</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 11:58:41 GMT</t>
+          <t>Wed, 29 Apr 2026 10:39:06 GMT</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMickFVX3lxTE04SGV5SWFVcWllYWVpcDluNHhaLTlJSU5Jamw5Q192YklxWnByNFp6RDFXRzBzYUE1dnZvUjVvTnJWWjdPUlpKLVFmTWloRjJHbmFkb1FBQjF1QjU0NktYT1pVUWJkTzNPWGtuSk0xZG0zZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNaVNQeWVUYkdyQ2xxOVRmc2xqN0NZalNOa082OVA2UjNxbzJsMlNkbU92RUN4QUVOY2R6SVZ6SENMQ2tSeHBRTXFMYm8wYVpyTl91TGxZYXZtdUlQTFAwLUplZm1uSzJpdFdsdXppMkhKNjg0ZkRiQ2R6U0o1M2x4MjVQaEgzUXBrX295NHRhWm1XcXRmNFpzQzJVUWNkV2tzSXc2aS05M2llUktRWnc?oc=5</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3059,38 +3059,38 @@
         </is>
       </c>
       <c r="K48" s="1" t="n">
-        <v>46141.49908564815</v>
+        <v>46141.44381944444</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Access Disruption Ingolstadt German</t>
+          <t>Access Disruption Ingolstadt English (fallback)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+          <t>("Ingolstadt" OR "A9 autobahn" OR "A8 autobahn")</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Wegen Unfall auf A9: Sperrung zwischen Siders-Ost und Siders-West - Unfallmeldungen.ch</t>
+          <t>Viktoria Köln 1904 - FotMob</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Due to an accident on the A9: closure between Siders-East and Siders-West - accident reports.ch</t>
+          <t>Victoria Cologne 1904 - PhotoMob</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:39:16 GMT</t>
+          <t>Wed, 29 Apr 2026 07:23:08 GMT</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMipgFBVV95cUxNaDdvdlU1NHFzOVd1VUZDSGlNUmhYQ2pDYXRpeDVJSDBsQmZXY2tfUlZsNWtjY3BvTHJadnZaTVQwNVE4X2xGV2RoQ24yVkx3cG5XckhNblhZZExhMVVEX3JhbFBuS1NiU2NqYnVfVk5ZVWdERW81SnZSeWFvV3lLY1VkWHZGODhNT01QNkZ3R2NscjhnOWh0aEdzaVM0eTRHemNpN3R3?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMijgFBVV95cUxPUWdnTW54d0VmNlNJeUpBdEgxRDJOTWhQeUhETWtSVFlKck1jdmpWWlJ6c2o2YjhsbDlHWVdnZmFOTHNFUTRPZndRVllfYVRXenE0VDBpV3pxN3BtNjZ3dHBMZUoxN1RTcjhETUlNVC1KQmRCX0haNFN6RTRsS0hqa1dnSVkwTjBZU3puQUJ3?oc=5</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3100,52 +3100,52 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>en-GB</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GB</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>GB:en</t>
         </is>
       </c>
       <c r="K49" s="1" t="n">
-        <v>46141.44393518518</v>
+        <v>46141.30773148148</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Access Disruption Ingolstadt German</t>
+          <t>Access Disruption Fidenza Italian</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>("Ingolstadt" OR "A9" OR "A8" OR "B9") AND (Sperrung OR Stau OR Unfall OR Protest OR Blockade OR Evakuierung OR Streckensperrung OR Polizeieinsatz) AND -Audi AND -Auto AND -Wetter AND -Sport</t>
+          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Wegen Unfall auf A2: Verkehrsbehinderung zwischen Beckenried und Buochs - Unfallmeldungen.ch</t>
+          <t>Incidente oggi in A13, autostrada nel caos per un camion ribaltato: tratto chiuso per ore e code - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Due to an accident on the A2: traffic obstruction between Beckenried and Buochs ​​- accident reports.ch</t>
+          <t>Accident today on the A13, highway in chaos due to an overturned truck: section closed for hours and queues - Il Resto del Carlino</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:39:06 GMT</t>
+          <t>Wed, 29 Apr 2026 10:57:48 GMT</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxNaVNQeWVUYkdyQ2xxOVRmc2xqN0NZalNOa082OVA2UjNxbzJsMlNkbU92RUN4QUVOY2R6SVZ6SENMQ2tSeHBRTXFMYm8wYVpyTl91TGxZYXZtdUlQTFAwLUplZm1uSzJpdFdsdXppMkhKNjg0ZkRiQ2R6U0o1M2x4MjVQaEgzUXBrX295NHRhWm1XcXRmNFpzQzJVUWNkV2tzSXc2aS05M2llUktRWnc?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTmZqWkZKQXlfTF9JbldkRXY4bUphTHB5dktsdDBqbk0yRTdyek8wM1JuSnhlM2xtYUZaNE9iSy1HN0ZqbWloVlRvV3VqZFY3VWJ4UWJ1b0JTVnV2RDVwVklMMW1tZVJqQXp1c3ZjMV8xWnQxNWJ1TkR3U1NCWEwxSA?oc=5</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
@@ -3155,21 +3155,21 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>de</t>
+          <t>it</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>DE:de</t>
+          <t>IT:it</t>
         </is>
       </c>
       <c r="K50" s="1" t="n">
-        <v>46141.44381944444</v>
+        <v>46141.45680555556</v>
       </c>
     </row>
     <row r="51">
@@ -3185,22 +3185,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Incidente oggi in A13, autostrada nel caos per un camion ribaltato: tratto chiuso per ore e code - Il Resto del Carlino</t>
+          <t>Autostrada A24, chiusura notturna della tratta L’Aquila Ovest-Tornimparte - ConfineLive</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Accident today on the A13, highway in chaos due to an overturned truck: section closed for hours and queues - Il Resto del Carlino</t>
+          <t>A24 motorway, night closure of the L'Aquila West-Tornimparte section - ConfineLive</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 10:57:48 GMT</t>
+          <t>Wed, 29 Apr 2026 09:00:32 GMT</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMigAFBVV95cUxQTmZqWkZKQXlfTF9JbldkRXY4bUphTHB5dktsdDBqbk0yRTdyek8wM1JuSnhlM2xtYUZaNE9iSy1HN0ZqbWloVlRvV3VqZFY3VWJ4UWJ1b0JTVnV2RDVwVklMMW1tZVJqQXp1c3ZjMV8xWnQxNWJ1TkR3U1NCWEwxSA?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcUgyNDVTVjhzdUxDOW95VUU5aVdqdk5wNEpULUlELWg1V0tPX29ZUFNfaDI1WUs3ZnBhaTFfNGE0VmNCTkFjYzBUTk1EVU5helBWQjV1UEIwNl9nRmVrQlkzM19uWUl4WWcyQ2FZTXNCSU5PNWRLSDVfajhwMVFseVB1LU1KTGhNVVdDS0xyOVhPUHpheDl2WVNUbUZKM0lK?oc=5</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -3224,7 +3224,7 @@
         </is>
       </c>
       <c r="K51" s="1" t="n">
-        <v>46141.45680555556</v>
+        <v>46141.37537037037</v>
       </c>
     </row>
     <row r="52">
@@ -3240,22 +3240,22 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Autostrada A24, chiusura notturna della tratta L’Aquila Ovest-Tornimparte - ConfineLive</t>
+          <t>Incidente sull’A13 a Occhiobello: autotreno si ribalta, autostrada chiusa in direzione nord - La Piazza Web</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>A24 motorway, night closure of the L'Aquila West-Tornimparte section - ConfineLive</t>
+          <t>Accident on the A13 in Occhiobello: lorry overturns, motorway closed heading north - La Piazza Web</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 09:00:32 GMT</t>
+          <t>Wed, 29 Apr 2026 07:22:00 GMT</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMioAFBVV95cUxQcUgyNDVTVjhzdUxDOW95VUU5aVdqdk5wNEpULUlELWg1V0tPX29ZUFNfaDI1WUs3ZnBhaTFfNGE0VmNCTkFjYzBUTk1EVU5helBWQjV1UEIwNl9nRmVrQlkzM19uWUl4WWcyQ2FZTXNCSU5PNWRLSDVfajhwMVFseVB1LU1KTGhNVVdDS0xyOVhPUHpheDl2WVNUbUZKM0lK?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUUlnZTI5SGI1SHNvTFAyNzBQeE01VWVtUkxWcWVrU3N5clA3UEhUSXJuc18taFdOX3k2QTVrckYyWlBXNjBubTJ2QlRZdWZkV1RWTWxvdkdyaFJRbmF6YzRsTnRHSTcydVp6cEx1RzVTR0E3N3VwV3pKZG5nM1VFekpfT3JoaUt0MFdmdGZRU1dwSGNQNE1oNFNrM0ZJNFFrbmE1NHVnWFZMU0VCNFpvZzhPYUtIQnZOdGt0SmNLTnRKM1ZMY3JYV1N1TTktNkFxTUtB?oc=5</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
@@ -3279,7 +3279,7 @@
         </is>
       </c>
       <c r="K52" s="1" t="n">
-        <v>46141.37537037037</v>
+        <v>46141.30694444444</v>
       </c>
     </row>
     <row r="53">
@@ -3295,22 +3295,22 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Incidente sull’A13 a Occhiobello: autotreno si ribalta, autostrada chiusa in direzione nord - La Piazza Web</t>
+          <t>Incidente A13 oggi: tratto riaperto ma 7 km di coda verso Padova - SICURAUTO.it</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Accident on the A13 in Occhiobello: lorry overturns, motorway closed heading north - La Piazza Web</t>
+          <t>A13 accident today: section reopened but 7 km of queue towards Padua - SICURAUTO.it</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:22:00 GMT</t>
+          <t>Wed, 29 Apr 2026 07:45:00 GMT</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMi0wFBVV95cUxQUUlnZTI5SGI1SHNvTFAyNzBQeE01VWVtUkxWcWVrU3N5clA3UEhUSXJuc18taFdOX3k2QTVrckYyWlBXNjBubTJ2QlRZdWZkV1RWTWxvdkdyaFJRbmF6YzRsTnRHSTcydVp6cEx1RzVTR0E3N3VwV3pKZG5nM1VFekpfT3JoaUt0MFdmdGZRU1dwSGNQNE1oNFNrM0ZJNFFrbmE1NHVnWFZMU0VCNFpvZzhPYUtIQnZOdGt0SmNLTnRKM1ZMY3JYV1N1TTktNkFxTUtB?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVTRGSzY4bW5XYjN4QVdrVHBJdUFXQmhPelBiWHduV2lPTkJVUkY1SlFOMUNFekxuQWUwY3R0WXY2cTRrVmd1Zi1NMGNMZnBkUW5xLTZvOXVvNTk5T0xadHEtdnlHMnB3SmpHc0dsRFlHZG5zYkFhRVBzcG85cDBSN29KOUNUMXpfT0xaMkxlM1I4azJfM1NpTjNRZkVRXzhEOHZUbGtIdWoxZw?oc=5</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
@@ -3334,7 +3334,7 @@
         </is>
       </c>
       <c r="K53" s="1" t="n">
-        <v>46141.30694444444</v>
+        <v>46141.32291666666</v>
       </c>
     </row>
     <row r="54">
@@ -3350,22 +3350,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Incidente A13 oggi: tratto riaperto ma 7 km di coda verso Padova - SICURAUTO.it</t>
+          <t>Incidente sull’autostrada A2 Salerno-Reggio, scontro con auto ribaltata: 4 feriti - Fanpage</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>A13 accident today: section reopened but 7 km of queue towards Padua - SICURAUTO.it</t>
+          <t>Accident on the A2 Salerno-Reggio motorway, collision with overturned car: 4 injured - Fanpage</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 07:45:00 GMT</t>
+          <t>Wed, 29 Apr 2026 12:34:33 GMT</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMiqgFBVV95cUxQVTRGSzY4bW5XYjN4QVdrVHBJdUFXQmhPelBiWHduV2lPTkJVUkY1SlFOMUNFekxuQWUwY3R0WXY2cTRrVmd1Zi1NMGNMZnBkUW5xLTZvOXVvNTk5T0xadHEtdnlHMnB3SmpHc0dsRFlHZG5zYkFhRVBzcG85cDBSN29KOUNUMXpfT0xaMkxlM1I4azJfM1NpTjNRZkVRXzhEOHZUbGtIdWoxZw?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSjlHZGVBeksyakZRRXFUaGRvTFBFTVVlWTE5X2x2QXl2aHFtZGRJM0ItMkNpWlh3RHVQS0lvY2RuelMtTHY5ZkNZVG5NTGpZVWdFSHlQSkpUR2toY0w4bU1NZWk5MVVQR0dCZm9UUzZmb255VnBuLVBoMTY0Y0lMZmpYTnZfaGNzSzJpLTc5RGxSelU5LTdsQ3F2eTBuUTBJbjVkSU54b0gtcUdQcVE?oc=5</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
@@ -3389,7 +3389,7 @@
         </is>
       </c>
       <c r="K54" s="1" t="n">
-        <v>46141.32291666666</v>
+        <v>46141.52399305555</v>
       </c>
     </row>
     <row r="55">
@@ -3405,22 +3405,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Incidente sull’autostrada A2 Salerno-Reggio, scontro con auto ribaltata: 4 feriti - Fanpage</t>
+          <t>Palermo, incidente con 5 feriti in via Nicoletti: chiuso lo svincolo Sferracavallo dell’A29 - Meridionews</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Accident on the A2 Salerno-Reggio motorway, collision with overturned car: 4 injured - Fanpage</t>
+          <t>Palermo, accident with 5 injured in via Nicoletti: the Sferracavallo junction of the A29 closed - Meridionews</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wed, 29 Apr 2026 12:34:33 GMT</t>
+          <t>Wed, 29 Apr 2026 08:12:30 GMT</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>https://news.google.com/rss/articles/CBMirgFBVV95cUxPSjlHZGVBeksyakZRRXFUaGRvTFBFTVVlWTE5X2x2QXl2aHFtZGRJM0ItMkNpWlh3RHVQS0lvY2RuelMtTHY5ZkNZVG5NTGpZVWdFSHlQSkpUR2toY0w4bU1NZWk5MVVQR0dCZm9UUzZmb255VnBuLVBoMTY0Y0lMZmpYTnZfaGNzSzJpLTc5RGxSelU5LTdsQ3F2eTBuUTBJbjVkSU54b0gtcUdQcVE?oc=5</t>
+          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBQdGZPT3BZX05EYnI4Zm0tMXRMM0cteWZJVWl6azQteDI4X3ZaRDZDcDFYWnV0eUx0SnN0Nmo0WmlkbWZrYTJCRWZaRHY5SmNPbVJTYW03YVVULTlqNHE0cWlDQWp5Zw?oc=5</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
@@ -3444,61 +3444,6 @@
         </is>
       </c>
       <c r="K55" s="1" t="n">
-        <v>46141.52399305555</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Access Disruption Fidenza Italian</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>("Fidenza" OR "Parma" OR "A1" OR "autostrada") AND (chiusura OR interruzione OR protesta OR blocco OR evacuazione OR incidente OR ritardo OR "strada chiusa" OR sciopero) AND -calcio AND -meteo</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Palermo, incidente con 5 feriti in via Nicoletti: chiuso lo svincolo Sferracavallo dell’A29 - Meridionews</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Palermo, accident with 5 injured in via Nicoletti: the Sferracavallo junction of the A29 closed - Meridionews</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr">
-        <is>
-          <t>Wed, 29 Apr 2026 08:12:30 GMT</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>https://news.google.com/rss/articles/CBMiZkFVX3lxTFBQdGZPT3BZX05EYnI4Zm0tMXRMM0cteWZJVWl6azQteDI4X3ZaRDZDcDFYWnV0eUx0SnN0Nmo0WmlkbWZrYTJCRWZaRHY5SmNPbVJTYW03YVVULTlqNHE0cWlDQWp5Zw?oc=5</t>
-        </is>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>google_rss</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>it</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>IT:it</t>
-        </is>
-      </c>
-      <c r="K56" s="1" t="n">
         <v>46141.34201388889</v>
       </c>
     </row>
